--- a/artfynd/A 21850-2024 artfynd.xlsx
+++ b/artfynd/A 21850-2024 artfynd.xlsx
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118001192</v>
+        <v>118001187</v>
       </c>
       <c r="B11" t="n">
-        <v>78480</v>
+        <v>90517</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,21 +1712,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>448426</v>
+        <v>448471</v>
       </c>
       <c r="R11" t="n">
-        <v>7033663</v>
+        <v>7033641</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118001187</v>
+        <v>118001192</v>
       </c>
       <c r="B12" t="n">
-        <v>90517</v>
+        <v>78480</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1824,21 +1824,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1848,10 +1848,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448471</v>
+        <v>448426</v>
       </c>
       <c r="R12" t="n">
-        <v>7033641</v>
+        <v>7033663</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2032,7 +2032,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118001204</v>
+        <v>118001203</v>
       </c>
       <c r="B14" t="n">
         <v>78480</v>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448408</v>
+        <v>448420</v>
       </c>
       <c r="R14" t="n">
-        <v>7033793</v>
+        <v>7033755</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,7 +2144,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118001203</v>
+        <v>118001204</v>
       </c>
       <c r="B15" t="n">
         <v>78480</v>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448420</v>
+        <v>448408</v>
       </c>
       <c r="R15" t="n">
-        <v>7033755</v>
+        <v>7033793</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2816,7 +2816,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118001214</v>
+        <v>118001216</v>
       </c>
       <c r="B21" t="n">
         <v>78480</v>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448498</v>
+        <v>448556</v>
       </c>
       <c r="R21" t="n">
-        <v>7034008</v>
+        <v>7034106</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2928,10 +2928,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118001202</v>
+        <v>118001214</v>
       </c>
       <c r="B22" t="n">
-        <v>97753</v>
+        <v>78480</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2940,25 +2940,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448415</v>
+        <v>448498</v>
       </c>
       <c r="R22" t="n">
-        <v>7033756</v>
+        <v>7034008</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3040,10 +3040,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118001235</v>
+        <v>118001202</v>
       </c>
       <c r="B23" t="n">
-        <v>104914</v>
+        <v>97753</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221725</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448503</v>
+        <v>448415</v>
       </c>
       <c r="R23" t="n">
-        <v>7033771</v>
+        <v>7033756</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,10 +3152,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118001216</v>
+        <v>118001235</v>
       </c>
       <c r="B24" t="n">
-        <v>78480</v>
+        <v>104914</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3164,25 +3164,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>448556</v>
+        <v>448503</v>
       </c>
       <c r="R24" t="n">
-        <v>7034106</v>
+        <v>7033771</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3264,10 +3264,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118001195</v>
+        <v>118001226</v>
       </c>
       <c r="B25" t="n">
-        <v>79561</v>
+        <v>97857</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3276,25 +3276,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448419</v>
+        <v>448533</v>
       </c>
       <c r="R25" t="n">
-        <v>7033726</v>
+        <v>7033865</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3376,10 +3376,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118001226</v>
+        <v>118001195</v>
       </c>
       <c r="B26" t="n">
-        <v>97857</v>
+        <v>79561</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3388,25 +3388,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3416,10 +3416,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448533</v>
+        <v>448419</v>
       </c>
       <c r="R26" t="n">
-        <v>7033865</v>
+        <v>7033726</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -5523,10 +5523,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118001239</v>
+        <v>118001225</v>
       </c>
       <c r="B45" t="n">
-        <v>98170</v>
+        <v>97753</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5539,21 +5539,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5563,10 +5563,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>448505</v>
+        <v>448533</v>
       </c>
       <c r="R45" t="n">
-        <v>7033744</v>
+        <v>7033866</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5635,10 +5635,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118001225</v>
+        <v>118001239</v>
       </c>
       <c r="B46" t="n">
-        <v>97753</v>
+        <v>98170</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5651,21 +5651,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>219880</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>448533</v>
+        <v>448505</v>
       </c>
       <c r="R46" t="n">
-        <v>7033866</v>
+        <v>7033744</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 21850-2024 artfynd.xlsx
+++ b/artfynd/A 21850-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118001224</v>
+        <v>118001195</v>
       </c>
       <c r="B3" t="n">
-        <v>79562</v>
+        <v>79561</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,21 +816,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448546</v>
+        <v>448419</v>
       </c>
       <c r="R3" t="n">
-        <v>7033901</v>
+        <v>7033726</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118001236</v>
+        <v>118001186</v>
       </c>
       <c r="B4" t="n">
-        <v>79597</v>
+        <v>97857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448497</v>
+        <v>448485</v>
       </c>
       <c r="R4" t="n">
-        <v>7033751</v>
+        <v>7033674</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118001208</v>
+        <v>118001232</v>
       </c>
       <c r="B5" t="n">
-        <v>90499</v>
+        <v>77417</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,21 +1040,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448458</v>
+        <v>448497</v>
       </c>
       <c r="R5" t="n">
-        <v>7033913</v>
+        <v>7033792</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118001191</v>
+        <v>118001221</v>
       </c>
       <c r="B6" t="n">
-        <v>104914</v>
+        <v>74584</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,25 +1148,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221725</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448414</v>
+        <v>448560</v>
       </c>
       <c r="R6" t="n">
-        <v>7033632</v>
+        <v>7034026</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118001222</v>
+        <v>118001203</v>
       </c>
       <c r="B7" t="n">
-        <v>79597</v>
+        <v>78480</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,25 +1260,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448560</v>
+        <v>448420</v>
       </c>
       <c r="R7" t="n">
-        <v>7034020</v>
+        <v>7033755</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118001232</v>
+        <v>118001190</v>
       </c>
       <c r="B8" t="n">
-        <v>77417</v>
+        <v>104914</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,25 +1372,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>221725</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1400,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448497</v>
+        <v>448429</v>
       </c>
       <c r="R8" t="n">
-        <v>7033792</v>
+        <v>7033590</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118001215</v>
+        <v>118001228</v>
       </c>
       <c r="B9" t="n">
-        <v>77417</v>
+        <v>104914</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,25 +1484,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>221725</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448515</v>
+        <v>448533</v>
       </c>
       <c r="R9" t="n">
-        <v>7034079</v>
+        <v>7033863</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118001197</v>
+        <v>118001208</v>
       </c>
       <c r="B10" t="n">
-        <v>97857</v>
+        <v>90499</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,25 +1596,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>448400</v>
+        <v>448458</v>
       </c>
       <c r="R10" t="n">
-        <v>7033710</v>
+        <v>7033913</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118001187</v>
+        <v>118001210</v>
       </c>
       <c r="B11" t="n">
-        <v>90517</v>
+        <v>78480</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,21 +1712,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>448471</v>
+        <v>448469</v>
       </c>
       <c r="R11" t="n">
-        <v>7033641</v>
+        <v>7033936</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118001192</v>
+        <v>118001206</v>
       </c>
       <c r="B12" t="n">
-        <v>78480</v>
+        <v>104914</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,25 +1820,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1848,10 +1848,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448426</v>
+        <v>448450</v>
       </c>
       <c r="R12" t="n">
-        <v>7033663</v>
+        <v>7033907</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118001205</v>
+        <v>118001191</v>
       </c>
       <c r="B13" t="n">
-        <v>79562</v>
+        <v>104914</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,25 +1932,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>221725</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448403</v>
+        <v>448414</v>
       </c>
       <c r="R13" t="n">
-        <v>7033818</v>
+        <v>7033632</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118001203</v>
+        <v>118001205</v>
       </c>
       <c r="B14" t="n">
-        <v>78480</v>
+        <v>79562</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2048,21 +2048,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448420</v>
+        <v>448403</v>
       </c>
       <c r="R14" t="n">
-        <v>7033755</v>
+        <v>7033818</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118001204</v>
+        <v>118001194</v>
       </c>
       <c r="B15" t="n">
-        <v>78480</v>
+        <v>97753</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2156,25 +2156,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448408</v>
+        <v>448448</v>
       </c>
       <c r="R15" t="n">
-        <v>7033793</v>
+        <v>7033738</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,10 +2256,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118001188</v>
+        <v>118001198</v>
       </c>
       <c r="B16" t="n">
-        <v>78480</v>
+        <v>90464</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2268,25 +2268,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448453</v>
+        <v>448385</v>
       </c>
       <c r="R16" t="n">
-        <v>7033608</v>
+        <v>7033724</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,10 +2368,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118001217</v>
+        <v>118001224</v>
       </c>
       <c r="B17" t="n">
-        <v>77417</v>
+        <v>79562</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2384,21 +2384,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>448562</v>
+        <v>448546</v>
       </c>
       <c r="R17" t="n">
-        <v>7034100</v>
+        <v>7033901</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,10 +2480,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118001209</v>
+        <v>118001226</v>
       </c>
       <c r="B18" t="n">
-        <v>79521</v>
+        <v>97857</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2496,21 +2496,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229497</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>448459</v>
+        <v>448533</v>
       </c>
       <c r="R18" t="n">
-        <v>7033911</v>
+        <v>7033865</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2592,10 +2592,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118001221</v>
+        <v>118001216</v>
       </c>
       <c r="B19" t="n">
-        <v>74584</v>
+        <v>78480</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2608,21 +2608,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2632,10 +2632,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448560</v>
+        <v>448556</v>
       </c>
       <c r="R19" t="n">
-        <v>7034026</v>
+        <v>7034106</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2704,10 +2704,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118001194</v>
+        <v>118001220</v>
       </c>
       <c r="B20" t="n">
-        <v>97753</v>
+        <v>78480</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2716,25 +2716,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448448</v>
+        <v>448552</v>
       </c>
       <c r="R20" t="n">
-        <v>7033738</v>
+        <v>7034021</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2816,10 +2816,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118001216</v>
+        <v>118001189</v>
       </c>
       <c r="B21" t="n">
-        <v>78480</v>
+        <v>97857</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2828,25 +2828,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448556</v>
+        <v>448453</v>
       </c>
       <c r="R21" t="n">
-        <v>7034106</v>
+        <v>7033607</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3040,10 +3040,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118001202</v>
+        <v>118001204</v>
       </c>
       <c r="B23" t="n">
-        <v>97753</v>
+        <v>78480</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3052,25 +3052,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448415</v>
+        <v>448408</v>
       </c>
       <c r="R23" t="n">
-        <v>7033756</v>
+        <v>7033793</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,10 +3152,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118001235</v>
+        <v>118001225</v>
       </c>
       <c r="B24" t="n">
-        <v>104914</v>
+        <v>97753</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3168,21 +3168,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221725</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>448503</v>
+        <v>448533</v>
       </c>
       <c r="R24" t="n">
-        <v>7033771</v>
+        <v>7033866</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3264,10 +3264,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118001226</v>
+        <v>118001192</v>
       </c>
       <c r="B25" t="n">
-        <v>97857</v>
+        <v>78480</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3276,25 +3276,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448533</v>
+        <v>448426</v>
       </c>
       <c r="R25" t="n">
-        <v>7033865</v>
+        <v>7033663</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3376,10 +3376,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118001195</v>
+        <v>118001209</v>
       </c>
       <c r="B26" t="n">
-        <v>79561</v>
+        <v>79521</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3388,25 +3388,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3416,10 +3416,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448419</v>
+        <v>448459</v>
       </c>
       <c r="R26" t="n">
-        <v>7033726</v>
+        <v>7033911</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3609,10 +3609,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118001210</v>
+        <v>118001230</v>
       </c>
       <c r="B28" t="n">
-        <v>78480</v>
+        <v>79561</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3625,21 +3625,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>448469</v>
+        <v>448498</v>
       </c>
       <c r="R28" t="n">
-        <v>7033936</v>
+        <v>7033804</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3721,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118001189</v>
+        <v>118001236</v>
       </c>
       <c r="B29" t="n">
-        <v>97857</v>
+        <v>79597</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3737,21 +3737,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>448453</v>
+        <v>448497</v>
       </c>
       <c r="R29" t="n">
-        <v>7033607</v>
+        <v>7033751</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3833,10 +3833,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118001223</v>
+        <v>118001193</v>
       </c>
       <c r="B30" t="n">
-        <v>79562</v>
+        <v>77417</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3849,21 +3849,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>448541</v>
+        <v>448425</v>
       </c>
       <c r="R30" t="n">
-        <v>7033952</v>
+        <v>7033662</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3945,10 +3945,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118001201</v>
+        <v>118001196</v>
       </c>
       <c r="B31" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3961,34 +3961,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Öretjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>448377</v>
+        <v>448411</v>
       </c>
       <c r="R31" t="n">
-        <v>7033755</v>
+        <v>7033687</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4020,7 +4025,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4030,7 +4035,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4057,10 +4067,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118001230</v>
+        <v>118001187</v>
       </c>
       <c r="B32" t="n">
-        <v>79561</v>
+        <v>90517</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4073,21 +4083,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4097,10 +4107,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>448498</v>
+        <v>448471</v>
       </c>
       <c r="R32" t="n">
-        <v>7033804</v>
+        <v>7033641</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4132,7 +4142,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4142,7 +4152,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4169,10 +4179,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118001231</v>
+        <v>118001217</v>
       </c>
       <c r="B33" t="n">
-        <v>79562</v>
+        <v>77417</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4185,21 +4195,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4209,10 +4219,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>448498</v>
+        <v>448562</v>
       </c>
       <c r="R33" t="n">
-        <v>7033802</v>
+        <v>7034100</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4244,7 +4254,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4254,7 +4264,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4281,10 +4291,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118001199</v>
+        <v>118001215</v>
       </c>
       <c r="B34" t="n">
-        <v>79596</v>
+        <v>77417</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4293,25 +4303,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>228579</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4321,10 +4331,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>448383</v>
+        <v>448515</v>
       </c>
       <c r="R34" t="n">
-        <v>7033725</v>
+        <v>7034079</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4356,7 +4366,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4366,7 +4376,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4393,10 +4403,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118001227</v>
+        <v>118001235</v>
       </c>
       <c r="B35" t="n">
-        <v>98170</v>
+        <v>104914</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4409,21 +4419,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219880</v>
+        <v>221725</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4433,10 +4443,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>448533</v>
+        <v>448503</v>
       </c>
       <c r="R35" t="n">
-        <v>7033863</v>
+        <v>7033771</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4468,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4478,7 +4488,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4505,10 +4515,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118001185</v>
+        <v>118001240</v>
       </c>
       <c r="B36" t="n">
-        <v>98170</v>
+        <v>97857</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4521,21 +4531,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219880</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4545,10 +4555,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>448500</v>
+        <v>448516</v>
       </c>
       <c r="R36" t="n">
-        <v>7033697</v>
+        <v>7033739</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4580,7 +4590,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4590,7 +4600,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4617,10 +4627,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118001206</v>
+        <v>118001222</v>
       </c>
       <c r="B37" t="n">
-        <v>104914</v>
+        <v>79597</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4633,21 +4643,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221725</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4657,10 +4667,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>448450</v>
+        <v>448560</v>
       </c>
       <c r="R37" t="n">
-        <v>7033907</v>
+        <v>7034020</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4692,7 +4702,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4702,7 +4712,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4729,10 +4739,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118001219</v>
+        <v>118001185</v>
       </c>
       <c r="B38" t="n">
-        <v>97857</v>
+        <v>98170</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4745,21 +4755,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>219880</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4769,10 +4779,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>448564</v>
+        <v>448500</v>
       </c>
       <c r="R38" t="n">
-        <v>7034057</v>
+        <v>7033697</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4804,7 +4814,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4814,7 +4824,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4841,10 +4851,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118001196</v>
+        <v>118001199</v>
       </c>
       <c r="B39" t="n">
-        <v>57287</v>
+        <v>79596</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4853,43 +4863,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Öretjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>448411</v>
+        <v>448383</v>
       </c>
       <c r="R39" t="n">
-        <v>7033687</v>
+        <v>7033725</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4921,7 +4926,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4931,12 +4936,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4963,10 +4963,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118001186</v>
+        <v>118001231</v>
       </c>
       <c r="B40" t="n">
-        <v>97857</v>
+        <v>79562</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4975,25 +4975,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5003,10 +5003,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>448485</v>
+        <v>448498</v>
       </c>
       <c r="R40" t="n">
-        <v>7033674</v>
+        <v>7033802</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5075,10 +5075,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118001200</v>
+        <v>118001227</v>
       </c>
       <c r="B41" t="n">
-        <v>79561</v>
+        <v>98170</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5087,25 +5087,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>448381</v>
+        <v>448533</v>
       </c>
       <c r="R41" t="n">
-        <v>7033724</v>
+        <v>7033863</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5187,10 +5187,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118001240</v>
+        <v>118001239</v>
       </c>
       <c r="B42" t="n">
-        <v>97857</v>
+        <v>98170</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5203,21 +5203,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221952</v>
+        <v>219880</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>448516</v>
+        <v>448505</v>
       </c>
       <c r="R42" t="n">
-        <v>7033739</v>
+        <v>7033744</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5299,10 +5299,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118001190</v>
+        <v>118001202</v>
       </c>
       <c r="B43" t="n">
-        <v>104914</v>
+        <v>97753</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5315,21 +5315,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221725</v>
+        <v>219790</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5339,10 +5339,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>448429</v>
+        <v>448415</v>
       </c>
       <c r="R43" t="n">
-        <v>7033590</v>
+        <v>7033756</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5411,10 +5411,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118001193</v>
+        <v>118001212</v>
       </c>
       <c r="B44" t="n">
-        <v>77417</v>
+        <v>79597</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5423,25 +5423,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>448425</v>
+        <v>448497</v>
       </c>
       <c r="R44" t="n">
-        <v>7033662</v>
+        <v>7033960</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5523,10 +5523,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118001225</v>
+        <v>118001229</v>
       </c>
       <c r="B45" t="n">
-        <v>97753</v>
+        <v>79562</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5535,25 +5535,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219790</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5563,10 +5563,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>448533</v>
+        <v>448537</v>
       </c>
       <c r="R45" t="n">
-        <v>7033866</v>
+        <v>7033821</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5635,10 +5635,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118001239</v>
+        <v>118001197</v>
       </c>
       <c r="B46" t="n">
-        <v>98170</v>
+        <v>97857</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5651,21 +5651,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219880</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>448505</v>
+        <v>448400</v>
       </c>
       <c r="R46" t="n">
-        <v>7033744</v>
+        <v>7033710</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5747,10 +5747,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118001198</v>
+        <v>118001223</v>
       </c>
       <c r="B47" t="n">
-        <v>90464</v>
+        <v>79562</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5759,25 +5759,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>448385</v>
+        <v>448541</v>
       </c>
       <c r="R47" t="n">
-        <v>7033724</v>
+        <v>7033952</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5859,10 +5859,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118001212</v>
+        <v>118001188</v>
       </c>
       <c r="B48" t="n">
-        <v>79597</v>
+        <v>78480</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5871,25 +5871,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>448497</v>
+        <v>448453</v>
       </c>
       <c r="R48" t="n">
-        <v>7033960</v>
+        <v>7033608</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5971,10 +5971,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118001229</v>
+        <v>118001201</v>
       </c>
       <c r="B49" t="n">
-        <v>79562</v>
+        <v>78480</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5987,21 +5987,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>448537</v>
+        <v>448377</v>
       </c>
       <c r="R49" t="n">
-        <v>7033821</v>
+        <v>7033755</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6083,10 +6083,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118001220</v>
+        <v>118001200</v>
       </c>
       <c r="B50" t="n">
-        <v>78480</v>
+        <v>79561</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6099,21 +6099,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6123,10 +6123,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>448552</v>
+        <v>448381</v>
       </c>
       <c r="R50" t="n">
-        <v>7034021</v>
+        <v>7033724</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6195,10 +6195,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118001228</v>
+        <v>118001219</v>
       </c>
       <c r="B51" t="n">
-        <v>104914</v>
+        <v>97857</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6211,21 +6211,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6235,10 +6235,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>448533</v>
+        <v>448564</v>
       </c>
       <c r="R51" t="n">
-        <v>7033863</v>
+        <v>7034057</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 21850-2024 artfynd.xlsx
+++ b/artfynd/A 21850-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>118001195</v>
       </c>
       <c r="B3" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118001186</v>
+        <v>118001206</v>
       </c>
       <c r="B4" t="n">
-        <v>97857</v>
+        <v>104916</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448485</v>
+        <v>448450</v>
       </c>
       <c r="R4" t="n">
-        <v>7033674</v>
+        <v>7033907</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118001232</v>
+        <v>118001223</v>
       </c>
       <c r="B5" t="n">
-        <v>77417</v>
+        <v>79564</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,21 +1040,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448497</v>
+        <v>448541</v>
       </c>
       <c r="R5" t="n">
-        <v>7033792</v>
+        <v>7033952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118001221</v>
+        <v>118001216</v>
       </c>
       <c r="B6" t="n">
-        <v>74584</v>
+        <v>78482</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,21 +1152,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448560</v>
+        <v>448556</v>
       </c>
       <c r="R6" t="n">
-        <v>7034026</v>
+        <v>7034106</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118001203</v>
+        <v>118001220</v>
       </c>
       <c r="B7" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448420</v>
+        <v>448552</v>
       </c>
       <c r="R7" t="n">
-        <v>7033755</v>
+        <v>7034021</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118001190</v>
+        <v>118001212</v>
       </c>
       <c r="B8" t="n">
-        <v>104914</v>
+        <v>79599</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,21 +1376,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221725</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1400,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448429</v>
+        <v>448497</v>
       </c>
       <c r="R8" t="n">
-        <v>7033590</v>
+        <v>7033960</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118001228</v>
+        <v>118001235</v>
       </c>
       <c r="B9" t="n">
-        <v>104914</v>
+        <v>104916</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448533</v>
+        <v>448503</v>
       </c>
       <c r="R9" t="n">
-        <v>7033863</v>
+        <v>7033771</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118001208</v>
+        <v>118001221</v>
       </c>
       <c r="B10" t="n">
-        <v>90499</v>
+        <v>74586</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,21 +1600,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>448458</v>
+        <v>448560</v>
       </c>
       <c r="R10" t="n">
-        <v>7033913</v>
+        <v>7034026</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118001210</v>
+        <v>118001224</v>
       </c>
       <c r="B11" t="n">
-        <v>78480</v>
+        <v>79564</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,21 +1712,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>448469</v>
+        <v>448546</v>
       </c>
       <c r="R11" t="n">
-        <v>7033936</v>
+        <v>7033901</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118001206</v>
+        <v>118001193</v>
       </c>
       <c r="B12" t="n">
-        <v>104914</v>
+        <v>77419</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,25 +1820,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221725</v>
+        <v>228579</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1848,10 +1848,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448450</v>
+        <v>448425</v>
       </c>
       <c r="R12" t="n">
-        <v>7033907</v>
+        <v>7033662</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118001191</v>
+        <v>118001215</v>
       </c>
       <c r="B13" t="n">
-        <v>104914</v>
+        <v>77419</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,25 +1932,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221725</v>
+        <v>228579</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448414</v>
+        <v>448515</v>
       </c>
       <c r="R13" t="n">
-        <v>7033632</v>
+        <v>7034079</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118001205</v>
+        <v>118001222</v>
       </c>
       <c r="B14" t="n">
-        <v>79562</v>
+        <v>79599</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,25 +2044,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448403</v>
+        <v>448560</v>
       </c>
       <c r="R14" t="n">
-        <v>7033818</v>
+        <v>7034020</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118001194</v>
+        <v>118001205</v>
       </c>
       <c r="B15" t="n">
-        <v>97753</v>
+        <v>79564</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2156,25 +2156,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448448</v>
+        <v>448403</v>
       </c>
       <c r="R15" t="n">
-        <v>7033738</v>
+        <v>7033818</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,10 +2256,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118001198</v>
+        <v>118001208</v>
       </c>
       <c r="B16" t="n">
-        <v>90464</v>
+        <v>90501</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2268,25 +2268,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448385</v>
+        <v>448458</v>
       </c>
       <c r="R16" t="n">
-        <v>7033724</v>
+        <v>7033913</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,10 +2368,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118001224</v>
+        <v>118001185</v>
       </c>
       <c r="B17" t="n">
-        <v>79562</v>
+        <v>98172</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2380,25 +2380,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>219880</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>448546</v>
+        <v>448500</v>
       </c>
       <c r="R17" t="n">
-        <v>7033901</v>
+        <v>7033697</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,10 +2480,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118001226</v>
+        <v>118001228</v>
       </c>
       <c r="B18" t="n">
-        <v>97857</v>
+        <v>104916</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2496,21 +2496,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2523,7 +2523,7 @@
         <v>448533</v>
       </c>
       <c r="R18" t="n">
-        <v>7033865</v>
+        <v>7033863</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118001216</v>
+        <v>118001230</v>
       </c>
       <c r="B19" t="n">
-        <v>78480</v>
+        <v>79563</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2608,21 +2608,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2632,10 +2632,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448556</v>
+        <v>448498</v>
       </c>
       <c r="R19" t="n">
-        <v>7034106</v>
+        <v>7033804</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2704,10 +2704,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118001220</v>
+        <v>118001232</v>
       </c>
       <c r="B20" t="n">
-        <v>78480</v>
+        <v>77419</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2720,21 +2720,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448552</v>
+        <v>448497</v>
       </c>
       <c r="R20" t="n">
-        <v>7034021</v>
+        <v>7033792</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2816,10 +2816,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118001189</v>
+        <v>118001187</v>
       </c>
       <c r="B21" t="n">
-        <v>97857</v>
+        <v>90519</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2828,25 +2828,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448453</v>
+        <v>448471</v>
       </c>
       <c r="R21" t="n">
-        <v>7033607</v>
+        <v>7033641</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2928,10 +2928,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118001214</v>
+        <v>118001237</v>
       </c>
       <c r="B22" t="n">
-        <v>78480</v>
+        <v>57441</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2944,34 +2944,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Öretjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448498</v>
+        <v>448507</v>
       </c>
       <c r="R22" t="n">
-        <v>7034008</v>
+        <v>7033742</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3003,7 +3012,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3013,7 +3022,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3040,10 +3049,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118001204</v>
+        <v>118001229</v>
       </c>
       <c r="B23" t="n">
-        <v>78480</v>
+        <v>79564</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3056,21 +3065,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3080,10 +3089,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448408</v>
+        <v>448537</v>
       </c>
       <c r="R23" t="n">
-        <v>7033793</v>
+        <v>7033821</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3115,7 +3124,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3125,7 +3134,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,10 +3161,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118001225</v>
+        <v>118001198</v>
       </c>
       <c r="B24" t="n">
-        <v>97753</v>
+        <v>90466</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3168,21 +3177,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3192,10 +3201,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>448533</v>
+        <v>448385</v>
       </c>
       <c r="R24" t="n">
-        <v>7033866</v>
+        <v>7033724</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3227,7 +3236,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3237,7 +3246,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3264,10 +3273,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118001192</v>
+        <v>118001188</v>
       </c>
       <c r="B25" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3304,10 +3313,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448426</v>
+        <v>448453</v>
       </c>
       <c r="R25" t="n">
-        <v>7033663</v>
+        <v>7033608</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3339,7 +3348,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3349,7 +3358,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3376,10 +3385,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118001209</v>
+        <v>118001227</v>
       </c>
       <c r="B26" t="n">
-        <v>79521</v>
+        <v>98172</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3392,21 +3401,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>219880</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3416,10 +3425,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448459</v>
+        <v>448533</v>
       </c>
       <c r="R26" t="n">
-        <v>7033911</v>
+        <v>7033863</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3451,7 +3460,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3461,7 +3470,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3488,10 +3497,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118001237</v>
+        <v>118001219</v>
       </c>
       <c r="B27" t="n">
-        <v>57440</v>
+        <v>97859</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3500,47 +3509,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Öretjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>448507</v>
+        <v>448564</v>
       </c>
       <c r="R27" t="n">
-        <v>7033742</v>
+        <v>7034057</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3609,10 +3609,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118001230</v>
+        <v>118001189</v>
       </c>
       <c r="B28" t="n">
-        <v>79561</v>
+        <v>97859</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3621,25 +3621,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>448498</v>
+        <v>448453</v>
       </c>
       <c r="R28" t="n">
-        <v>7033804</v>
+        <v>7033607</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3721,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118001236</v>
+        <v>118001196</v>
       </c>
       <c r="B29" t="n">
-        <v>79597</v>
+        <v>57288</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3733,38 +3733,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Öretjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>448497</v>
+        <v>448411</v>
       </c>
       <c r="R29" t="n">
-        <v>7033751</v>
+        <v>7033687</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3796,7 +3801,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3806,7 +3811,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3833,10 +3843,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118001193</v>
+        <v>118001204</v>
       </c>
       <c r="B30" t="n">
-        <v>77417</v>
+        <v>78482</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3849,21 +3859,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3873,10 +3883,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>448425</v>
+        <v>448408</v>
       </c>
       <c r="R30" t="n">
-        <v>7033662</v>
+        <v>7033793</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3908,7 +3918,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3918,7 +3928,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3945,10 +3955,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118001196</v>
+        <v>118001199</v>
       </c>
       <c r="B31" t="n">
-        <v>57287</v>
+        <v>79598</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3957,43 +3967,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Öretjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>448411</v>
+        <v>448383</v>
       </c>
       <c r="R31" t="n">
-        <v>7033687</v>
+        <v>7033725</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4025,7 +4030,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4035,12 +4040,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4067,10 +4067,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118001187</v>
+        <v>118001203</v>
       </c>
       <c r="B32" t="n">
-        <v>90517</v>
+        <v>78482</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4083,21 +4083,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>448471</v>
+        <v>448420</v>
       </c>
       <c r="R32" t="n">
-        <v>7033641</v>
+        <v>7033755</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4179,10 +4179,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118001217</v>
+        <v>118001214</v>
       </c>
       <c r="B33" t="n">
-        <v>77417</v>
+        <v>78482</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4195,21 +4195,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>448562</v>
+        <v>448498</v>
       </c>
       <c r="R33" t="n">
-        <v>7034100</v>
+        <v>7034008</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4291,10 +4291,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118001215</v>
+        <v>118001226</v>
       </c>
       <c r="B34" t="n">
-        <v>77417</v>
+        <v>97859</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4303,25 +4303,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228579</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>448515</v>
+        <v>448533</v>
       </c>
       <c r="R34" t="n">
-        <v>7034079</v>
+        <v>7033865</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4403,10 +4403,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118001235</v>
+        <v>118001240</v>
       </c>
       <c r="B35" t="n">
-        <v>104914</v>
+        <v>97859</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4419,21 +4419,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>448503</v>
+        <v>448516</v>
       </c>
       <c r="R35" t="n">
-        <v>7033771</v>
+        <v>7033739</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4515,10 +4515,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118001240</v>
+        <v>118001209</v>
       </c>
       <c r="B36" t="n">
-        <v>97857</v>
+        <v>79523</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4531,21 +4531,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>229497</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>448516</v>
+        <v>448459</v>
       </c>
       <c r="R36" t="n">
-        <v>7033739</v>
+        <v>7033911</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4627,10 +4627,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118001222</v>
+        <v>118001192</v>
       </c>
       <c r="B37" t="n">
-        <v>79597</v>
+        <v>78482</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4639,25 +4639,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>448560</v>
+        <v>448426</v>
       </c>
       <c r="R37" t="n">
-        <v>7034020</v>
+        <v>7033663</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4739,10 +4739,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118001185</v>
+        <v>118001201</v>
       </c>
       <c r="B38" t="n">
-        <v>98170</v>
+        <v>78482</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4751,25 +4751,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>448500</v>
+        <v>448377</v>
       </c>
       <c r="R38" t="n">
-        <v>7033697</v>
+        <v>7033755</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4851,10 +4851,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118001199</v>
+        <v>118001217</v>
       </c>
       <c r="B39" t="n">
-        <v>79596</v>
+        <v>77419</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4863,25 +4863,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>448383</v>
+        <v>448562</v>
       </c>
       <c r="R39" t="n">
-        <v>7033725</v>
+        <v>7034100</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4963,10 +4963,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118001231</v>
+        <v>118001210</v>
       </c>
       <c r="B40" t="n">
-        <v>79562</v>
+        <v>78482</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4979,21 +4979,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5003,10 +5003,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>448498</v>
+        <v>448469</v>
       </c>
       <c r="R40" t="n">
-        <v>7033802</v>
+        <v>7033936</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5075,10 +5075,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118001227</v>
+        <v>118001231</v>
       </c>
       <c r="B41" t="n">
-        <v>98170</v>
+        <v>79564</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5087,25 +5087,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219880</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>448533</v>
+        <v>448498</v>
       </c>
       <c r="R41" t="n">
-        <v>7033863</v>
+        <v>7033802</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5187,10 +5187,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118001239</v>
+        <v>118001225</v>
       </c>
       <c r="B42" t="n">
-        <v>98170</v>
+        <v>97755</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5203,21 +5203,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>448505</v>
+        <v>448533</v>
       </c>
       <c r="R42" t="n">
-        <v>7033744</v>
+        <v>7033866</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5299,10 +5299,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118001202</v>
+        <v>118001191</v>
       </c>
       <c r="B43" t="n">
-        <v>97753</v>
+        <v>104916</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5315,21 +5315,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219790</v>
+        <v>221725</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5339,10 +5339,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>448415</v>
+        <v>448414</v>
       </c>
       <c r="R43" t="n">
-        <v>7033756</v>
+        <v>7033632</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5411,10 +5411,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118001212</v>
+        <v>118001239</v>
       </c>
       <c r="B44" t="n">
-        <v>79597</v>
+        <v>98172</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5427,21 +5427,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>219880</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>448497</v>
+        <v>448505</v>
       </c>
       <c r="R44" t="n">
-        <v>7033960</v>
+        <v>7033744</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5523,10 +5523,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118001229</v>
+        <v>118001186</v>
       </c>
       <c r="B45" t="n">
-        <v>79562</v>
+        <v>97859</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5535,25 +5535,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5563,10 +5563,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>448537</v>
+        <v>448485</v>
       </c>
       <c r="R45" t="n">
-        <v>7033821</v>
+        <v>7033674</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5635,10 +5635,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118001197</v>
+        <v>118001190</v>
       </c>
       <c r="B46" t="n">
-        <v>97857</v>
+        <v>104916</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5651,21 +5651,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>448400</v>
+        <v>448429</v>
       </c>
       <c r="R46" t="n">
-        <v>7033710</v>
+        <v>7033590</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5747,10 +5747,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118001223</v>
+        <v>118001236</v>
       </c>
       <c r="B47" t="n">
-        <v>79562</v>
+        <v>79599</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5759,25 +5759,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>448541</v>
+        <v>448497</v>
       </c>
       <c r="R47" t="n">
-        <v>7033952</v>
+        <v>7033751</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5859,10 +5859,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118001188</v>
+        <v>118001194</v>
       </c>
       <c r="B48" t="n">
-        <v>78480</v>
+        <v>97755</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5871,25 +5871,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>448453</v>
+        <v>448448</v>
       </c>
       <c r="R48" t="n">
-        <v>7033608</v>
+        <v>7033738</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5971,10 +5971,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118001201</v>
+        <v>118001202</v>
       </c>
       <c r="B49" t="n">
-        <v>78480</v>
+        <v>97755</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5983,25 +5983,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>448377</v>
+        <v>448415</v>
       </c>
       <c r="R49" t="n">
-        <v>7033755</v>
+        <v>7033756</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6083,10 +6083,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118001200</v>
+        <v>118001197</v>
       </c>
       <c r="B50" t="n">
-        <v>79561</v>
+        <v>97859</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6095,25 +6095,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6123,10 +6123,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>448381</v>
+        <v>448400</v>
       </c>
       <c r="R50" t="n">
-        <v>7033724</v>
+        <v>7033710</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6195,10 +6195,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118001219</v>
+        <v>118001200</v>
       </c>
       <c r="B51" t="n">
-        <v>97857</v>
+        <v>79563</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6207,25 +6207,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6235,10 +6235,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>448564</v>
+        <v>448381</v>
       </c>
       <c r="R51" t="n">
-        <v>7034057</v>
+        <v>7033724</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 21850-2024 artfynd.xlsx
+++ b/artfynd/A 21850-2024 artfynd.xlsx
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118001221</v>
+        <v>118001193</v>
       </c>
       <c r="B10" t="n">
-        <v>74586</v>
+        <v>77419</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,21 +1600,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>308</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>448560</v>
+        <v>448425</v>
       </c>
       <c r="R10" t="n">
-        <v>7034026</v>
+        <v>7033662</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118001224</v>
+        <v>118001215</v>
       </c>
       <c r="B11" t="n">
-        <v>79564</v>
+        <v>77419</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,21 +1712,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>448546</v>
+        <v>448515</v>
       </c>
       <c r="R11" t="n">
-        <v>7033901</v>
+        <v>7034079</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118001193</v>
+        <v>118001221</v>
       </c>
       <c r="B12" t="n">
-        <v>77419</v>
+        <v>74586</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1824,21 +1824,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228579</v>
+        <v>308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1848,10 +1848,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448425</v>
+        <v>448560</v>
       </c>
       <c r="R12" t="n">
-        <v>7033662</v>
+        <v>7034026</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118001215</v>
+        <v>118001224</v>
       </c>
       <c r="B13" t="n">
-        <v>77419</v>
+        <v>79564</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1936,21 +1936,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448515</v>
+        <v>448546</v>
       </c>
       <c r="R13" t="n">
-        <v>7034079</v>
+        <v>7033901</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2480,10 +2480,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118001228</v>
+        <v>118001232</v>
       </c>
       <c r="B18" t="n">
-        <v>104916</v>
+        <v>77419</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2492,25 +2492,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221725</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>448533</v>
+        <v>448497</v>
       </c>
       <c r="R18" t="n">
-        <v>7033863</v>
+        <v>7033792</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2592,10 +2592,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118001230</v>
+        <v>118001228</v>
       </c>
       <c r="B19" t="n">
-        <v>79563</v>
+        <v>104916</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2604,25 +2604,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>221725</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2632,10 +2632,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448498</v>
+        <v>448533</v>
       </c>
       <c r="R19" t="n">
-        <v>7033804</v>
+        <v>7033863</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2704,10 +2704,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118001232</v>
+        <v>118001230</v>
       </c>
       <c r="B20" t="n">
-        <v>77419</v>
+        <v>79563</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2720,21 +2720,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448497</v>
+        <v>448498</v>
       </c>
       <c r="R20" t="n">
-        <v>7033792</v>
+        <v>7033804</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -4403,10 +4403,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118001240</v>
+        <v>118001192</v>
       </c>
       <c r="B35" t="n">
-        <v>97859</v>
+        <v>78482</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4415,25 +4415,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>448516</v>
+        <v>448426</v>
       </c>
       <c r="R35" t="n">
-        <v>7033739</v>
+        <v>7033663</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4515,10 +4515,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118001209</v>
+        <v>118001201</v>
       </c>
       <c r="B36" t="n">
-        <v>79523</v>
+        <v>78482</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4527,25 +4527,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>448459</v>
+        <v>448377</v>
       </c>
       <c r="R36" t="n">
-        <v>7033911</v>
+        <v>7033755</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4627,10 +4627,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118001192</v>
+        <v>118001240</v>
       </c>
       <c r="B37" t="n">
-        <v>78482</v>
+        <v>97859</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4639,25 +4639,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>448426</v>
+        <v>448516</v>
       </c>
       <c r="R37" t="n">
-        <v>7033663</v>
+        <v>7033739</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4739,10 +4739,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118001201</v>
+        <v>118001209</v>
       </c>
       <c r="B38" t="n">
-        <v>78482</v>
+        <v>79523</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4751,25 +4751,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>448377</v>
+        <v>448459</v>
       </c>
       <c r="R38" t="n">
-        <v>7033755</v>
+        <v>7033911</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5411,10 +5411,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118001239</v>
+        <v>118001186</v>
       </c>
       <c r="B44" t="n">
-        <v>98172</v>
+        <v>97859</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5427,21 +5427,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219880</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>448505</v>
+        <v>448485</v>
       </c>
       <c r="R44" t="n">
-        <v>7033744</v>
+        <v>7033674</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5523,10 +5523,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118001186</v>
+        <v>118001190</v>
       </c>
       <c r="B45" t="n">
-        <v>97859</v>
+        <v>104916</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5539,21 +5539,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5563,10 +5563,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>448485</v>
+        <v>448429</v>
       </c>
       <c r="R45" t="n">
-        <v>7033674</v>
+        <v>7033590</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5635,10 +5635,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118001190</v>
+        <v>118001239</v>
       </c>
       <c r="B46" t="n">
-        <v>104916</v>
+        <v>98172</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5651,21 +5651,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221725</v>
+        <v>219880</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>448429</v>
+        <v>448505</v>
       </c>
       <c r="R46" t="n">
-        <v>7033590</v>
+        <v>7033744</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5747,10 +5747,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118001236</v>
+        <v>118001194</v>
       </c>
       <c r="B47" t="n">
-        <v>79599</v>
+        <v>97755</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5763,21 +5763,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>448497</v>
+        <v>448448</v>
       </c>
       <c r="R47" t="n">
-        <v>7033751</v>
+        <v>7033738</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5859,10 +5859,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118001194</v>
+        <v>118001236</v>
       </c>
       <c r="B48" t="n">
-        <v>97755</v>
+        <v>79599</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5875,21 +5875,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>448448</v>
+        <v>448497</v>
       </c>
       <c r="R48" t="n">
-        <v>7033738</v>
+        <v>7033751</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD48" t="b">
